--- a/results/errors/residuals_diagnostics.xlsx
+++ b/results/errors/residuals_diagnostics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,6 +1248,6270 @@
         <v>0.18679</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-614947.76923</v>
+      </c>
+      <c r="E29" t="n">
+        <v>196539.94146</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.14728</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2484</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-234865.38462</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1417167.93724</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.04319</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>305.34615</v>
+      </c>
+      <c r="E31" t="n">
+        <v>248.92538</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.4634</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-13.69692</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.82891</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.10203</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.85754</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.34526</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.157</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.08346000000000001</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.54722</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.03664</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.18768</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.31405</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-45.27729</v>
+      </c>
+      <c r="E36" t="n">
+        <v>82.7179</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6142300000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.01224</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6.45395</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.59117</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.53523</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-11.00231</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.71171</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.21672</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.72787</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.94899</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2152.4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1076.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.94929</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.06408</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-242524.30769</v>
+      </c>
+      <c r="E41" t="n">
+        <v>190121.52299</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>-6.48462</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.66386</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.47313</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.60933</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.18388</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-1289489.23077</v>
+      </c>
+      <c r="E44" t="n">
+        <v>815237.83506</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-2.016</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.11978</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.85628</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.00063</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-1.11096</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.18679</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-2.87125</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.93097</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.01068</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-12483.74392</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6119.45947</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.00267</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.02651</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.56746</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0449</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.34904</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.14374</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.00031</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.00449</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.06494999999999999</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.54569</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3166846077.32183</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3682067862.42168</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.17603</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5.30537</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.25959</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.24581</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.3043</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.68429</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.09057999999999999</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.09018</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.01175</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.15326</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.15568</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-13.79942</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.93097</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.01068</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-2.87125</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.93097</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.01068</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-3.59887</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.9729</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.03506</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-39937.41059</v>
+      </c>
+      <c r="E59" t="n">
+        <v>6119.45947</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.00267</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-12483.74392</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6119.45947</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.00267</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-10597.74392</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6448.54672</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.47074</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.01134</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>-0.45369</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.56746</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0449</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>-0.02651</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.56746</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0449</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.04306</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.62871</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.06413000000000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>-4.90245</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.14374</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.00031</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>-0.34904</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.14374</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.00031</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>-0.20943</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.57663</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.02577</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-0.49207</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.06494999999999999</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.54569</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.00449</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.06494999999999999</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.54569</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.07604</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.09914000000000001</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.1848</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2976324292.93482</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3682067862.42168</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.17603</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>3166846077.32183</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3682067862.42168</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.17603</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>4098806954.65774</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3508445746.60007</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.53261</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.23682</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>-0.00426</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.25959</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.24581</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>5.30537</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.25959</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.24581</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.83591</v>
+      </c>
+      <c r="E76" t="n">
+        <v>8.316280000000001</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.04821</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>-8.88166</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.68429</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.09057999999999999</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.09018</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>-0.3043</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.68429</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.09057999999999999</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.09018</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>-1.08935</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.03855</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.96538</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.05736</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.15326</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.15568</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>-0.01175</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.15326</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.15568</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>-0.01021</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.00423</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.15513</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.69968</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>-2643260.26923</v>
+      </c>
+      <c r="E83" t="n">
+        <v>196539.94146</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.14728</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.2484</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>-614947.76923</v>
+      </c>
+      <c r="E84" t="n">
+        <v>196539.94146</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.14728</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.2484</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>-467409.30769</v>
+      </c>
+      <c r="E85" t="n">
+        <v>237977.05371</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.05235</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.96226</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>-463768.56829</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1417167.93724</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.04319</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>-234865.38462</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1417167.93724</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.04319</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>-2454470.92308</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1960233.05606</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.53987</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.78943</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1557.91554</v>
+      </c>
+      <c r="E89" t="n">
+        <v>248.92538</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.4634</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>305.34615</v>
+      </c>
+      <c r="E90" t="n">
+        <v>248.92538</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.4634</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>189.96923</v>
+      </c>
+      <c r="E91" t="n">
+        <v>238.57899</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.03955</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.40756</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>-11.85631</v>
+      </c>
+      <c r="E92" t="n">
+        <v>4.82891</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.10203</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>-13.69692</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4.82891</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.10203</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>-11.67538</v>
+      </c>
+      <c r="E94" t="n">
+        <v>5.26746</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.12805</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.26823</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>-1.1758</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.85754</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.34526</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.85754</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.34526</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.09188</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.70597</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>-1.89091</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.08346000000000001</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.54722</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>-0.157</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.08346000000000001</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.54722</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.08769</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.67374</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.67304</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.61003</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.18768</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.31405</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.03664</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.18768</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.31405</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.22865</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.21464</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.74951</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>35.42736</v>
+      </c>
+      <c r="E104" t="n">
+        <v>82.7179</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.6142300000000001</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.01224</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>-45.27729</v>
+      </c>
+      <c r="E105" t="n">
+        <v>82.7179</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.6142300000000001</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.01224</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>-278.83045</v>
+      </c>
+      <c r="E106" t="n">
+        <v>323.60205</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.06229</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>-49.05968</v>
+      </c>
+      <c r="E107" t="n">
+        <v>6.59117</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.53523</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>6.45395</v>
+      </c>
+      <c r="E108" t="n">
+        <v>6.59117</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.53523</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>-27.70378</v>
+      </c>
+      <c r="E109" t="n">
+        <v>31.03872</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.0702</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>-5.03925</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.71171</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.21672</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>-11.00231</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3.71171</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.21672</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>-9.967689999999999</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4.1266</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.76555</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.55549</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3.36191</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.94899</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.72787</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.94899</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.93582</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.08617</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.20283</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10108.71346</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1076.2</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.94929</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.06408</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2152.4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1076.2</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.94929</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.06408</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2767.34857</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1129.76941</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.08615</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.203</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>-1634397.14443</v>
+      </c>
+      <c r="E119" t="n">
+        <v>190121.52299</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>-242524.30769</v>
+      </c>
+      <c r="E120" t="n">
+        <v>190121.52299</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>-587965.30769</v>
+      </c>
+      <c r="E121" t="n">
+        <v>288202.04148</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.83087</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.94718</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>7.03355</v>
+      </c>
+      <c r="E122" t="n">
+        <v>3.66386</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.47313</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>-6.48462</v>
+      </c>
+      <c r="E123" t="n">
+        <v>3.66386</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.47313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>-7.45462</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4.62547</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.93689</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>-1.53333</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.18388</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.60933</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.18388</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.51106</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.24904</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.23972</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>-1400345.86538</v>
+      </c>
+      <c r="E128" t="n">
+        <v>815237.83506</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>-1289489.23077</v>
+      </c>
+      <c r="E129" t="n">
+        <v>815237.83506</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>-1287500.30769</v>
+      </c>
+      <c r="E130" t="n">
+        <v>815064.14982</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.57118</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>-4.66125</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1.11978</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.85628</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.00063</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>-2.016</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.11978</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.85628</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.00063</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>-2.14238</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.11949</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.73973</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.0007</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>-0.98942</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.18679</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>-1.11096</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.18679</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>-1.23086</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.7670400000000001</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.17909</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>-13.79942</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.93097</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.01068</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>-2.87125</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.93097</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.01068</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>-3.59887</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1.9729</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.03506</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.48892</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.07602</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.42397</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.83334</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>-39937.41059</v>
+      </c>
+      <c r="E141" t="n">
+        <v>6119.45947</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.00267</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>-12483.74392</v>
+      </c>
+      <c r="E142" t="n">
+        <v>6119.45947</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.00267</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>-10597.74392</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6448.54672</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.47074</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.01134</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>-3211.27584</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2493.5455</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.60839</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.71675</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>-0.45369</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.56746</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.0449</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>-0.02651</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.56746</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.0449</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.04306</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.62871</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.06413000000000001</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.23524</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.13534</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.00028</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>-4.90245</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.14374</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.00031</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>-0.34904</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.14374</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.00031</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>-0.20943</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.57663</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.02577</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1.68421</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.84732</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.98627</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.00171</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>-0.49207</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.06494999999999999</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.54569</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>-0.00449</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.06494999999999999</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.54569</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.07604</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.09914000000000001</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.1848</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.18591</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.14488</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.5779</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.24457</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2976324292.93482</v>
+      </c>
+      <c r="E157" t="n">
+        <v>3682067862.42168</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.17603</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>3166846077.32183</v>
+      </c>
+      <c r="E158" t="n">
+        <v>3682067862.42168</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.17603</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>4098806954.65774</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3508445746.60007</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.53261</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.23682</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>3214105017.03078</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3701742286.21411</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.19996</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.17429</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>-0.00426</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1.25959</v>
+      </c>
+      <c r="F161" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.24581</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>5.30537</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1.25959</v>
+      </c>
+      <c r="F162" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.24581</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>12.83591</v>
+      </c>
+      <c r="E163" t="n">
+        <v>8.316280000000001</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.04821</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>7.92337</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2.46785</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.24854</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.03607</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>-8.88166</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.68429</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.09057999999999999</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.09018</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>-0.3043</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.68429</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.09057999999999999</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.09018</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>-1.08935</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1.03855</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.96538</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2.6306</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1.91205</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.13278</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.00099</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>-0.05736</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.15326</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.15568</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>-0.01175</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.15326</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.15568</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>-0.01021</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.00423</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.15513</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.69968</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.01157</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.18328</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.00244</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>-2643260.26923</v>
+      </c>
+      <c r="E173" t="n">
+        <v>196539.94146</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.14728</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.2484</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>-614947.76923</v>
+      </c>
+      <c r="E174" t="n">
+        <v>196539.94146</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.14728</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.2484</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>-467409.30769</v>
+      </c>
+      <c r="E175" t="n">
+        <v>237977.05371</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.05235</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.96226</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>183945.84779</v>
+      </c>
+      <c r="E176" t="n">
+        <v>496199.97517</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.00464</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>-463768.56829</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1417167.93724</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.04319</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>-234865.38462</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1417167.93724</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.04319</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>-2454470.92308</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1960233.05606</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.53987</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.78943</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>-784999.17628</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1676731.89852</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.01602</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1557.91554</v>
+      </c>
+      <c r="E181" t="n">
+        <v>248.92538</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.4634</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>305.34615</v>
+      </c>
+      <c r="E182" t="n">
+        <v>248.92538</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.4634</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>189.96923</v>
+      </c>
+      <c r="E183" t="n">
+        <v>238.57899</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.03955</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.40756</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>-118.35801</v>
+      </c>
+      <c r="E184" t="n">
+        <v>381.99254</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.26627</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.44277</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>-11.85631</v>
+      </c>
+      <c r="E185" t="n">
+        <v>4.82891</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.10203</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>-13.69692</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4.82891</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.10203</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>-11.67538</v>
+      </c>
+      <c r="E187" t="n">
+        <v>5.26746</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.12805</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.26823</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>-16.51005</v>
+      </c>
+      <c r="E188" t="n">
+        <v>6.12223</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.02831</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>-1.1758</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.85754</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.34526</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.85754</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.34526</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0.09188</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.70597</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0.67975</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.22996</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.04503</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>-1.89091</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.08346000000000001</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.54722</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>-0.157</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.08346000000000001</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.54722</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>-0.08769</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.67374</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.67304</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0.84614</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.46942</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.61358</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.05412</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>-0.61003</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.18768</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.31405</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0.03664</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.18768</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.31405</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0.22865</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.21464</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.74951</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0.58052</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.05232</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>35.42736</v>
+      </c>
+      <c r="E201" t="n">
+        <v>82.7179</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.6142300000000001</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.01224</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>-45.27729</v>
+      </c>
+      <c r="E202" t="n">
+        <v>82.7179</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.6142300000000001</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.01224</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>-278.83045</v>
+      </c>
+      <c r="E203" t="n">
+        <v>323.60205</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.06229</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>-71.47387999999999</v>
+      </c>
+      <c r="E204" t="n">
+        <v>95.26575</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.00652</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>-49.05968</v>
+      </c>
+      <c r="E205" t="n">
+        <v>6.59117</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.53523</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>6.45395</v>
+      </c>
+      <c r="E206" t="n">
+        <v>6.59117</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.53523</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>-27.70378</v>
+      </c>
+      <c r="E207" t="n">
+        <v>31.03872</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.0702</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>-1.17554</v>
+      </c>
+      <c r="E208" t="n">
+        <v>9.089919999999999</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.02004</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.08838</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>-5.03925</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3.71171</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.21672</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>-11.00231</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.71171</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.21672</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>-9.967689999999999</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4.1266</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.76555</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.55549</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>-14.8071</v>
+      </c>
+      <c r="E212" t="n">
+        <v>5.37945</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.11673</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.03248</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>3.36191</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.94899</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>0.72787</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.94899</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0.93582</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.08617</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.20283</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>-0.17344</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.08674999999999999</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.95051</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.06431000000000001</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>10108.71346</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1076.2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.94929</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.06408</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>2152.4</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1076.2</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.94929</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.06408</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>2767.34857</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1129.76941</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.08615</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.203</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>-579.328</v>
+      </c>
+      <c r="E220" t="n">
+        <v>289.664</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.94929</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.06408</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>-1634397.14443</v>
+      </c>
+      <c r="E221" t="n">
+        <v>190121.52299</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>-242524.30769</v>
+      </c>
+      <c r="E222" t="n">
+        <v>190121.52299</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>-587965.30769</v>
+      </c>
+      <c r="E223" t="n">
+        <v>288202.04148</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.83087</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0.94718</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>181347.27564</v>
+      </c>
+      <c r="E224" t="n">
+        <v>63586.88887</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0.34352</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>7.03355</v>
+      </c>
+      <c r="E225" t="n">
+        <v>3.66386</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0.47313</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>-6.48462</v>
+      </c>
+      <c r="E226" t="n">
+        <v>3.66386</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.47313</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>-7.45462</v>
+      </c>
+      <c r="E227" t="n">
+        <v>4.62547</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.93689</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>-12.30774</v>
+      </c>
+      <c r="E228" t="n">
+        <v>5.1422</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.13525</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>-1.53333</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.18388</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>-0.60933</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0.18388</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>-0.51106</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.24904</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.23972</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>-0.51928</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.06412</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.22067</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>-1400345.86538</v>
+      </c>
+      <c r="E233" t="n">
+        <v>815237.83506</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>-1289489.23077</v>
+      </c>
+      <c r="E234" t="n">
+        <v>815237.83506</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>-1287500.30769</v>
+      </c>
+      <c r="E235" t="n">
+        <v>815064.14982</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.57118</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>-1089291.15234</v>
+      </c>
+      <c r="E236" t="n">
+        <v>708529.64008</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.52215</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.00038</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>-4.66125</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1.11978</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.85628</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.00063</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>-2.016</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1.11978</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.85628</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.00063</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>-2.14238</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1.11949</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.73973</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.0007</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>-0.76931</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.45361</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0.87135</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.00068</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>-0.98942</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.18679</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>-1.11096</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0.18679</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>-1.23086</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.7670400000000001</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0.17909</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>-1.18561</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.93377</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0.10388</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/errors/residuals_diagnostics.xlsx
+++ b/results/errors/residuals_diagnostics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G244"/>
+  <dimension ref="A1:G250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7512,6 +7512,180 @@
         <v>0.10388</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>-12486.03309</v>
+      </c>
+      <c r="E245" t="n">
+        <v>6119.45947</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0.00267</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>-12472.67709</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6117.80584</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0.00267</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>-0.02471</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0.56746</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0.0449</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>-0.03505</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.03541</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0.57983</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0.04508</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>-2.73121</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1.93097</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0.01068</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>-2.71822</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1.91923</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0.01021</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/errors/residuals_diagnostics.xlsx
+++ b/results/errors/residuals_diagnostics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G250"/>
+  <dimension ref="A1:G277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7686,6 +7686,789 @@
         <v>0.01021</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>-0.01078</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.03269</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0.98243</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>-0.06033</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.00797</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.14946</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>-14283.67288</v>
+      </c>
+      <c r="E253" t="n">
+        <v>60960.03258</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0.46185</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>-0.03507</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.13011</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0.22053</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0.97341</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>-0.03135</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.18513</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0.59646</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>-0.04072</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.10778</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0.8214900000000001</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0.34872</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>0.03463</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0.79923</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>0.00286</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0.9385</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>-0.1988</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1.33384</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0.23631</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0.21268</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>-1580.74692</v>
+      </c>
+      <c r="E260" t="n">
+        <v>3532.11804</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0.08702</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0.0277</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>0.04098</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.6748</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.95726</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0.2997</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>-0.00022</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.00431</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.95199</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0.25398</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>-23478.00307</v>
+      </c>
+      <c r="E263" t="n">
+        <v>242799.0502</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0.98766</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0.19021</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>-35736.82738</v>
+      </c>
+      <c r="E264" t="n">
+        <v>47544.26736</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0.82053</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>-0.04496</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0.88198</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0.41984</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>0.98354</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1.49629</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0.04073</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>-1.08468</v>
+      </c>
+      <c r="E267" t="n">
+        <v>7.18056</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0.49981</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0.02989</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>-53.56878</v>
+      </c>
+      <c r="E268" t="n">
+        <v>45.2855</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.79972</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0.11753</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>-0.83623</v>
+      </c>
+      <c r="E269" t="n">
+        <v>3.76193</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.7743</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0.93298</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>-1.85581</v>
+      </c>
+      <c r="E270" t="n">
+        <v>3.03897</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0.99649</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0.94784</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>-2.01766</v>
+      </c>
+      <c r="E271" t="n">
+        <v>3.85709</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.93033</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0.41359</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>-297971.8949</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1016059.47093</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.17134</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0.5212</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>-6.52308</v>
+      </c>
+      <c r="E273" t="n">
+        <v>318.99708</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0.58084</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0.57121</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>0.02879</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.17829</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1468626389.95404</v>
+      </c>
+      <c r="E275" t="n">
+        <v>2299978417.63823</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.89947</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0.85268</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>-0.00697</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.03831</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.98968</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0.09612</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>-0.04446</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.10617</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.97357</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0.82884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
